--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20212.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -76,73 +76,64 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
     <t>AQUINO</t>
   </si>
   <si>
-    <t>DOMINGUEZ</t>
+    <t>ALVAREZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MELANY NARAYANA</t>
-  </si>
-  <si>
     <t>BETSI JOSELIN</t>
   </si>
   <si>
-    <t>ZAYRA</t>
+    <t>PEDRO ANGEL</t>
   </si>
   <si>
     <t>EMMANUEL DAVID</t>
   </si>
   <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
     <t>RONALDO</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
   </si>
 </sst>
 </file>
@@ -917,7 +908,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -949,22 +940,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920134</v>
+        <v>21330051920032</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -972,22 +963,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920032</v>
+        <v>21330051920135</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -995,16 +986,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920038</v>
+        <v>21330051920043</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1013,44 +1004,44 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920043</v>
+        <v>21330051920141</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920147</v>
+        <v>21330051920143</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1059,21 +1050,21 @@
         <v>12</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920141</v>
+        <v>21330051920381</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1087,16 +1078,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920143</v>
+        <v>21330051920147</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1105,29 +1096,6 @@
         <v>12</v>
       </c>
       <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920381</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20212.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -76,15 +76,15 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>AQUINO</t>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>MARIN</t>
   </si>
   <si>
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -97,12 +97,12 @@
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
     <t>NAJERA</t>
   </si>
   <si>
@@ -115,13 +115,13 @@
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>BETSI JOSELIN</t>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
   </si>
   <si>
     <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
   </si>
   <si>
     <t>ALBERTO SHAKIB</t>
@@ -534,10 +534,10 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>24</v>
@@ -546,7 +546,7 @@
         <v>85.70999999999999</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -560,19 +560,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>82.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -586,19 +586,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>75.61</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -677,16 +677,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>60.71</v>
+      </c>
+      <c r="H2">
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -700,16 +703,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H3">
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -723,16 +729,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>41.46</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -746,16 +755,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>58.82</v>
+      </c>
+      <c r="H5">
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>
@@ -808,19 +820,19 @@
         <v>28</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
         <v>4</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
       <c r="F2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>85.70999999999999</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -834,19 +846,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>82.14</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -860,19 +872,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>75.61</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -908,7 +920,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -940,13 +952,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920032</v>
+        <v>21330051920112</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
@@ -955,7 +967,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -963,7 +975,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920135</v>
+        <v>21330051920126</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
@@ -975,10 +987,10 @@
         <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -986,39 +998,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920043</v>
+        <v>21330051920126</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920141</v>
+        <v>21330051920135</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1027,21 +1039,21 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920143</v>
+        <v>21330051920141</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1055,16 +1067,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920381</v>
+        <v>21330051920143</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1078,16 +1090,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920147</v>
+        <v>21330051920381</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1096,6 +1108,29 @@
         <v>12</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920147</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20212.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -79,9 +79,15 @@
     <t>CASTRO</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>MARIN</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
@@ -97,6 +103,9 @@
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -112,13 +121,16 @@
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>DIEGO</t>
   </si>
   <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
     <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
   </si>
   <si>
     <t>PEDRO ANGEL</t>
@@ -534,16 +546,16 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>85.70999999999999</v>
+        <v>92.86</v>
       </c>
       <c r="H2">
         <v>6.3</v>
@@ -560,19 +572,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>85.70999999999999</v>
+        <v>92.86</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -677,19 +689,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>60.71</v>
+        <v>82.14</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -703,19 +715,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -755,19 +767,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>58.82</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
   </sheetData>
@@ -820,16 +832,16 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>4</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>78.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H2">
         <v>6.2</v>
@@ -846,16 +858,16 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>78.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
         <v>6.7</v>
@@ -920,7 +932,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -958,10 +970,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -975,16 +987,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920126</v>
+        <v>21330051920391</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -998,16 +1010,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920126</v>
+        <v>21330051920391</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1021,22 +1033,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920135</v>
+        <v>21330051920126</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1044,62 +1056,62 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920141</v>
+        <v>21330051920126</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920143</v>
+        <v>21330051920057</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920381</v>
+        <v>21330051920135</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1113,16 +1125,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920147</v>
+        <v>21330051920141</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1131,6 +1143,75 @@
         <v>12</v>
       </c>
       <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920143</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920381</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920147</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20212.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -74,78 +74,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
   </si>
 </sst>
 </file>
@@ -572,10 +500,10 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>26</v>
@@ -598,19 +526,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>82.93000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -689,7 +617,7 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -715,10 +643,10 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>24</v>
@@ -741,19 +669,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>41.46</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -767,16 +695,16 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>64.70999999999999</v>
+        <v>70.59</v>
       </c>
       <c r="H5">
         <v>5.7</v>
@@ -835,16 +763,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>85.70999999999999</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -858,19 +786,19 @@
         <v>28</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
       <c r="F3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>85.70999999999999</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -884,19 +812,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>82.93000000000001</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -913,16 +841,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>70.59</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -932,7 +860,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -962,259 +890,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920112</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920391</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920391</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920126</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920126</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920057</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920135</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920141</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920143</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920381</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920147</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
